--- a/data/target_form/당진해나루쌀조공법인.xlsx
+++ b/data/target_form/당진해나루쌀조공법인.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ae7f7f815e37025b/문서/365건강농산/목표양식/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\skawl\PycharmProjects\365배포\data\target_form\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{659563D7-80C8-4D5C-8021-7AC798290759}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BCC24548-71C9-44EE-9070-915CE4F73429}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4D64F97-1FDB-43A3-8FFE-4F4D84778B1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="16090" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
   <si>
     <t>수량</t>
   </si>
@@ -77,15 +77,7 @@
   </si>
   <si>
     <t>번호</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>365건강농산</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>당진해나루쌀 조공법인   택배발송대장</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Chang kee reum</t>
@@ -143,7 +135,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -174,14 +166,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="24"/>
-      <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="맑은 고딕"/>
@@ -210,22 +194,6 @@
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
     <font>
       <sz val="10"/>
@@ -283,7 +251,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
@@ -296,7 +264,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -309,32 +277,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -355,10 +314,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -651,7 +606,7 @@
   <sheetPr codeName="1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q4"/>
+  <dimension ref="A1:Q3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="4.5" style="7" bestFit="1" customWidth="1"/>
@@ -673,163 +628,143 @@
     <col min="18" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:17" s="5" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B2" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="8" t="s">
+      <c r="D2" s="8">
+        <v>1</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" s="8" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" s="5" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>15</v>
-      </c>
+      <c r="K2" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2" s="8"/>
+      <c r="M2" s="9">
+        <v>2149040292</v>
+      </c>
+      <c r="N2" s="8"/>
+      <c r="O2" s="8"/>
+      <c r="P2" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q2" s="8"/>
     </row>
     <row r="3" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" s="9">
+      <c r="B3" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="8">
         <v>1</v>
       </c>
-      <c r="E3" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="K3" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="L3" s="9"/>
-      <c r="M3" s="10">
-        <v>2149040292</v>
-      </c>
-      <c r="N3" s="9"/>
-      <c r="O3" s="9"/>
-      <c r="P3" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q3" s="9"/>
-    </row>
-    <row r="4" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B4" s="9" t="s">
+      <c r="E3" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="F3" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="9">
-        <v>1</v>
-      </c>
-      <c r="E4" s="9" t="s">
+      <c r="H3" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="F4" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="G4" s="9" t="s">
+      <c r="I3" s="8"/>
+      <c r="J3" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="K3" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9" t="s">
+      <c r="L3" s="8"/>
+      <c r="M3" s="9">
+        <v>2149018388</v>
+      </c>
+      <c r="N3" s="8"/>
+      <c r="O3" s="8"/>
+      <c r="P3" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="K4" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="L4" s="9"/>
-      <c r="M4" s="10">
-        <v>2149018388</v>
-      </c>
-      <c r="N4" s="9"/>
-      <c r="O4" s="9"/>
-      <c r="P4" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q4" s="9"/>
+      <c r="Q3" s="8"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
-  </mergeCells>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <pageSetup paperSize="9" scale="79" orientation="landscape" r:id="rId1"/>
 </worksheet>
@@ -841,7 +776,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <sheetData/>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait" draft="1"/>
 </worksheet>
@@ -853,7 +788,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <sheetData/>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait" draft="1"/>
 </worksheet>
@@ -865,7 +800,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <sheetData/>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.74805557727813721" right="0.74805557727813721" top="0.98430556058883667" bottom="0.98430556058883667" header="0.51138889789581299" footer="0.51138889789581299"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait"/>
 </worksheet>
